--- a/60_Threshold_OUTPUT_REPORT/60_observation_roc_evaluations.xlsx
+++ b/60_Threshold_OUTPUT_REPORT/60_observation_roc_evaluations.xlsx
@@ -485,7 +485,7 @@
         <v>0.8554578168732507</v>
       </c>
       <c r="E2" t="n">
-        <v>0.272890843662535</v>
+        <v>0</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -716,7 +716,7 @@
         <v>0.9994002399040384</v>
       </c>
       <c r="E9" t="n">
-        <v>0.3052778888444622</v>
+        <v>0</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1241,7 +1241,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>0.0645741703318673</v>
+        <v>0</v>
       </c>
       <c r="E25" t="n">
         <v>0.9956017592962815</v>
@@ -1937,7 +1937,7 @@
         <v>0.9990003998400639</v>
       </c>
       <c r="E46" t="n">
-        <v>0.01439424230307873</v>
+        <v>0</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -1970,7 +1970,7 @@
         <v>0.9958016793282687</v>
       </c>
       <c r="E47" t="n">
-        <v>0.0001999200319872108</v>
+        <v>0</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
         <v>0.9962015193922431</v>
       </c>
       <c r="E49" t="n">
-        <v>0.1259496201519392</v>
+        <v>0</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -2168,7 +2168,7 @@
         <v>0.9956017592962815</v>
       </c>
       <c r="E53" t="n">
-        <v>0.5771691323470611</v>
+        <v>0</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -2198,7 +2198,7 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>0.0177928828468612</v>
+        <v>0</v>
       </c>
       <c r="E54" t="n">
         <v>0.9996001599360256</v>
